--- a/FTP/meta-data/test-data/test-data/06-test-source-xlsx.xlsx
+++ b/FTP/meta-data/test-data/test-data/06-test-source-xlsx.xlsx
@@ -1,26 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a4a2f0a0b0b35b4f/xlsx-data/udm/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\ftp-application\FTP\meta-data\test-data\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_79C876F25086C010B0C00D414842314401048F89" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0CBBFBA-5B0D-40A0-9DE6-3D1F5ABB85F5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D7161A-64C8-4E9D-ACC6-0ED805F5A56A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="yml-data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>#</t>
   </si>
@@ -83,6 +95,27 @@
   </si>
   <si>
     <t>078098-24-02234 dt. 16-12-2024 11:05:21by                   MITHLESH  PRASAD</t>
+  </si>
+  <si>
+    <t>excelDataConfig:</t>
+  </si>
+  <si>
+    <t>allowedApi:</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>appendCellDataIndex:</t>
+  </si>
+  <si>
+    <t>removeColumnConfig: [0,1,2]</t>
+  </si>
+  <si>
+    <t>yml-config-app-id:</t>
+  </si>
+  <si>
+    <t>- [0,-1]</t>
   </si>
 </sst>
 </file>
@@ -120,11 +153,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -140,10 +174,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -537,4 +567,53 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7694E3FF-B647-44E7-B6E2-BB6AC6440A13}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="str">
+        <f>CHAR(34) &amp;"update_excel_data_v2" &amp; CHAR(34)</f>
+        <v>"update_excel_data_v2"</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="D6" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>